--- a/docs/downloads/20260820_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260820_Johor_Teduh_Weekly_Update.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AF20"/>
+  <dimension ref="A2:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,10 @@
     <col width="9" customWidth="1" min="29" max="29"/>
     <col width="9" customWidth="1" min="30" max="30"/>
     <col width="9" customWidth="1" min="31" max="31"/>
-    <col width="46" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="46" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -565,8 +568,11 @@
       <c r="Z3" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="3" t="n">
         <v>46248</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>46255</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -711,22 +717,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AE4" s="6" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AF4" s="5" t="inlineStr">
+      <c r="AF4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AG4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AH4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AI4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -769,6 +790,9 @@
       <c r="AD5" s="8" t="n"/>
       <c r="AE5" s="8" t="n"/>
       <c r="AF5" s="8" t="n"/>
+      <c r="AG5" s="8" t="n"/>
+      <c r="AH5" s="8" t="n"/>
+      <c r="AI5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -872,20 +896,31 @@
         <f>AA6/$D$6</f>
         <v/>
       </c>
-      <c r="AC6" s="13">
+      <c r="AC6" s="11">
         <f>AD6-AA6</f>
         <v/>
       </c>
-      <c r="AD6" s="13" t="n">
+      <c r="AD6" s="11" t="n">
         <v>297</v>
       </c>
-      <c r="AE6" s="14">
+      <c r="AE6" s="12">
         <f>AD6/$D$6</f>
         <v/>
       </c>
-      <c r="AF6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 188, Block B: 109</t>
+      <c r="AF6" s="13">
+        <f>AG6-AD6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="13" t="n">
+        <v>302</v>
+      </c>
+      <c r="AH6" s="14">
+        <f>AG6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 189, Block B: 113</t>
         </is>
       </c>
     </row>
@@ -991,20 +1026,31 @@
         <f>AA7/$D$7</f>
         <v/>
       </c>
-      <c r="AC7" s="13">
+      <c r="AC7" s="11">
         <f>AD7-AA7</f>
         <v/>
       </c>
-      <c r="AD7" s="13" t="n">
+      <c r="AD7" s="11" t="n">
         <v>942</v>
       </c>
-      <c r="AE7" s="14">
+      <c r="AE7" s="12">
         <f>AD7/$D$7</f>
         <v/>
       </c>
-      <c r="AF7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 382, Block B: 367, Block C: 86, Block D: 107</t>
+      <c r="AF7" s="13">
+        <f>AG7-AD7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="13" t="n">
+        <v>954</v>
+      </c>
+      <c r="AH7" s="14">
+        <f>AG7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AI7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 389, Block B: 371, Block C: 86, Block D: 108</t>
         </is>
       </c>
     </row>
@@ -1110,20 +1156,31 @@
         <f>AA8/$D$8</f>
         <v/>
       </c>
-      <c r="AC8" s="13">
+      <c r="AC8" s="11">
         <f>AD8-AA8</f>
         <v/>
       </c>
-      <c r="AD8" s="13" t="n">
+      <c r="AD8" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="AE8" s="14">
+      <c r="AE8" s="12">
         <f>AD8/$D$8</f>
         <v/>
       </c>
-      <c r="AF8" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 47</t>
+      <c r="AF8" s="13">
+        <f>AG8-AD8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH8" s="14">
+        <f>AG8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AI8" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 48</t>
         </is>
       </c>
     </row>
@@ -1229,20 +1286,31 @@
         <f>AA9/$D$9</f>
         <v/>
       </c>
-      <c r="AC9" s="13">
+      <c r="AC9" s="11">
         <f>AD9-AA9</f>
         <v/>
       </c>
-      <c r="AD9" s="13" t="n">
+      <c r="AD9" s="11" t="n">
         <v>1052</v>
       </c>
-      <c r="AE9" s="14">
+      <c r="AE9" s="12">
         <f>AD9/$D$9</f>
         <v/>
       </c>
-      <c r="AF9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block 1A: 326, Block 1B: 340, Block 2A: 212, Block 2B: 174</t>
+      <c r="AF9" s="13">
+        <f>AG9-AD9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="13" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AH9" s="14">
+        <f>AG9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AI9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block 1A: 327, Block 1B: 340, Block 2A: 215, Block 2B: 176</t>
         </is>
       </c>
     </row>
@@ -1283,6 +1351,9 @@
       <c r="AD10" s="8" t="n"/>
       <c r="AE10" s="8" t="n"/>
       <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8" t="n"/>
+      <c r="AI10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1386,18 +1457,29 @@
         <f>AA11/$D$11</f>
         <v/>
       </c>
-      <c r="AC11" s="13">
+      <c r="AC11" s="11">
         <f>AD11-AA11</f>
         <v/>
       </c>
-      <c r="AD11" s="13" t="n">
+      <c r="AD11" s="11" t="n">
         <v>845</v>
       </c>
-      <c r="AE11" s="14">
+      <c r="AE11" s="12">
         <f>AD11/$D$11</f>
         <v/>
       </c>
-      <c r="AF11" s="10" t="inlineStr">
+      <c r="AF11" s="13">
+        <f>AG11-AD11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="13" t="n">
+        <v>845</v>
+      </c>
+      <c r="AH11" s="14">
+        <f>AG11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AI11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1505,20 +1587,31 @@
         <f>AA12/$D$12</f>
         <v/>
       </c>
-      <c r="AC12" s="13">
+      <c r="AC12" s="11">
         <f>AD12-AA12</f>
         <v/>
       </c>
-      <c r="AD12" s="13" t="n">
+      <c r="AD12" s="11" t="n">
         <v>1417</v>
       </c>
-      <c r="AE12" s="14">
+      <c r="AE12" s="12">
         <f>AD12/$D$12</f>
         <v/>
       </c>
-      <c r="AF12" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 446, Block B1: 231, Block B2: 284, Block D1: 168, Block D2: 288</t>
+      <c r="AF12" s="13">
+        <f>AG12-AD12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="13" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AH12" s="14">
+        <f>AG12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AI12" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 449, Block B1: 231, Block B2: 285, Block D1: 168, Block D2: 288</t>
         </is>
       </c>
     </row>
@@ -1624,20 +1717,31 @@
         <f>AA13/$D$13</f>
         <v/>
       </c>
-      <c r="AC13" s="13">
+      <c r="AC13" s="11">
         <f>AD13-AA13</f>
         <v/>
       </c>
-      <c r="AD13" s="13" t="n">
+      <c r="AD13" s="11" t="n">
         <v>990</v>
       </c>
-      <c r="AE13" s="14">
+      <c r="AE13" s="12">
         <f>AD13/$D$13</f>
         <v/>
       </c>
-      <c r="AF13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 401, Block B: 365, Block C: 224</t>
+      <c r="AF13" s="13">
+        <f>AG13-AD13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="AH13" s="14">
+        <f>AG13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AI13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 403, Block B: 369, Block C: 229</t>
         </is>
       </c>
     </row>
@@ -1743,20 +1847,31 @@
         <f>AA14/$D$14</f>
         <v/>
       </c>
-      <c r="AC14" s="13">
+      <c r="AC14" s="11">
         <f>AD14-AA14</f>
         <v/>
       </c>
-      <c r="AD14" s="13" t="n">
+      <c r="AD14" s="11" t="n">
         <v>731</v>
       </c>
-      <c r="AE14" s="14">
+      <c r="AE14" s="12">
         <f>AD14/$D$14</f>
         <v/>
       </c>
-      <c r="AF14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 488, Block B: 243</t>
+      <c r="AF14" s="13">
+        <f>AG14-AD14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="13" t="n">
+        <v>741</v>
+      </c>
+      <c r="AH14" s="14">
+        <f>AG14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AI14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 494, Block B: 247</t>
         </is>
       </c>
     </row>
@@ -1862,20 +1977,31 @@
         <f>AA15/$D$15</f>
         <v/>
       </c>
-      <c r="AC15" s="13">
+      <c r="AC15" s="11">
         <f>AD15-AA15</f>
         <v/>
       </c>
-      <c r="AD15" s="13" t="n">
+      <c r="AD15" s="11" t="n">
         <v>1391</v>
       </c>
-      <c r="AE15" s="14">
+      <c r="AE15" s="12">
         <f>AD15/$D$15</f>
         <v/>
       </c>
-      <c r="AF15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 725, Block B: 666</t>
+      <c r="AF15" s="13">
+        <f>AG15-AD15</f>
+        <v/>
+      </c>
+      <c r="AG15" s="13" t="n">
+        <v>1394</v>
+      </c>
+      <c r="AH15" s="14">
+        <f>AG15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AI15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 727, Block B: 667</t>
         </is>
       </c>
     </row>
@@ -1981,18 +2107,29 @@
         <f>AA16/$D$16</f>
         <v/>
       </c>
-      <c r="AC16" s="13">
+      <c r="AC16" s="11">
         <f>AD16-AA16</f>
         <v/>
       </c>
-      <c r="AD16" s="13" t="n">
+      <c r="AD16" s="11" t="n">
         <v>902</v>
       </c>
-      <c r="AE16" s="14">
+      <c r="AE16" s="12">
         <f>AD16/$D$16</f>
         <v/>
       </c>
-      <c r="AF16" s="10" t="inlineStr">
+      <c r="AF16" s="13">
+        <f>AG16-AD16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="13" t="n">
+        <v>906</v>
+      </c>
+      <c r="AH16" s="14">
+        <f>AG16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AI16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2100,10 +2237,13 @@
         <f>AA17/$D$17</f>
         <v/>
       </c>
-      <c r="AC17" s="13" t="n"/>
-      <c r="AD17" s="13" t="n"/>
-      <c r="AE17" s="14" t="n"/>
-      <c r="AF17" s="10" t="inlineStr">
+      <c r="AC17" s="11" t="n"/>
+      <c r="AD17" s="11" t="n"/>
+      <c r="AE17" s="12" t="n"/>
+      <c r="AF17" s="13" t="n"/>
+      <c r="AG17" s="13" t="n"/>
+      <c r="AH17" s="14" t="n"/>
+      <c r="AI17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -2211,20 +2351,31 @@
         <f>AA18/$D$18</f>
         <v/>
       </c>
-      <c r="AC18" s="13">
+      <c r="AC18" s="11">
         <f>AD18-AA18</f>
         <v/>
       </c>
-      <c r="AD18" s="13" t="n">
+      <c r="AD18" s="11" t="n">
         <v>714</v>
       </c>
-      <c r="AE18" s="14">
+      <c r="AE18" s="12">
         <f>AD18/$D$18</f>
         <v/>
       </c>
-      <c r="AF18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 432, Block B: 282</t>
+      <c r="AF18" s="13">
+        <f>AG18-AD18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="13" t="n">
+        <v>720</v>
+      </c>
+      <c r="AH18" s="14">
+        <f>AG18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AI18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 436, Block B: 284</t>
         </is>
       </c>
     </row>
@@ -2330,20 +2481,31 @@
         <f>AA19/$D$19</f>
         <v/>
       </c>
-      <c r="AC19" s="13">
+      <c r="AC19" s="11">
         <f>AD19-AA19</f>
         <v/>
       </c>
-      <c r="AD19" s="13" t="n">
+      <c r="AD19" s="11" t="n">
         <v>385</v>
       </c>
-      <c r="AE19" s="14">
+      <c r="AE19" s="12">
         <f>AD19/$D$19</f>
         <v/>
       </c>
-      <c r="AF19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 294, Block B: 91</t>
+      <c r="AF19" s="13">
+        <f>AG19-AD19</f>
+        <v/>
+      </c>
+      <c r="AG19" s="13" t="n">
+        <v>390</v>
+      </c>
+      <c r="AH19" s="14">
+        <f>AG19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 297, Block B: 93</t>
         </is>
       </c>
     </row>
@@ -2449,28 +2611,40 @@
         <f>AA20/$D$20</f>
         <v/>
       </c>
-      <c r="AC20" s="13">
+      <c r="AC20" s="11">
         <f>AD20-AA20</f>
         <v/>
       </c>
-      <c r="AD20" s="13" t="n">
+      <c r="AD20" s="11" t="n">
         <v>291</v>
       </c>
-      <c r="AE20" s="14">
+      <c r="AE20" s="12">
         <f>AD20/$D$20</f>
         <v/>
       </c>
-      <c r="AF20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 209, Block B: 82</t>
+      <c r="AF20" s="13">
+        <f>AG20-AD20</f>
+        <v/>
+      </c>
+      <c r="AG20" s="13" t="n">
+        <v>296</v>
+      </c>
+      <c r="AH20" s="14">
+        <f>AG20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AI20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 212, Block B: 84</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AF3:AH3"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H3:J3"/>
